--- a/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_by_Sample_Layer.xlsx
@@ -1274,10 +1274,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>21.593320612441</v>
+        <v>21.6004891333318</v>
       </c>
       <c r="H2" t="n">
-        <v>1.21283305713485</v>
+        <v>1.21342084119697</v>
       </c>
     </row>
     <row r="3">
@@ -1300,10 +1300,10 @@
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>17.4383623802787</v>
+        <v>17.4335608237773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.57404082297464</v>
+        <v>0.573903827456795</v>
       </c>
     </row>
     <row r="4">
@@ -1326,10 +1326,10 @@
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>15.6285124441035</v>
+        <v>15.6252452039893</v>
       </c>
       <c r="H4" t="n">
-        <v>2.15971300523427</v>
+        <v>2.15930845022779</v>
       </c>
     </row>
     <row r="5">
@@ -1352,10 +1352,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>8.36211780916747</v>
+        <v>8.36354044156639</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8880237394107</v>
+        <v>1.88837296899669</v>
       </c>
     </row>
     <row r="6">
@@ -1378,7 +1378,7 @@
         <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>6.0952094129783</v>
+        <v>6.09481794786706</v>
       </c>
       <c r="H6"/>
     </row>
@@ -1402,10 +1402,10 @@
         <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>3.90500227376959</v>
+        <v>3.90422965362823</v>
       </c>
       <c r="H7" t="n">
-        <v>0.266626492270157</v>
+        <v>0.266549307914427</v>
       </c>
     </row>
     <row r="8">
@@ -1428,10 +1428,10 @@
         <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>3.22608947813918</v>
+        <v>3.22543327786321</v>
       </c>
       <c r="H8" t="n">
-        <v>0.652462783436685</v>
+        <v>0.65231206138855</v>
       </c>
     </row>
     <row r="9">
@@ -1454,10 +1454,10 @@
         <v>66</v>
       </c>
       <c r="G9" t="n">
-        <v>3.01934852754756</v>
+        <v>3.02049654283758</v>
       </c>
       <c r="H9" t="n">
-        <v>0.739625173122029</v>
+        <v>0.739908294415527</v>
       </c>
     </row>
     <row r="10">
@@ -1480,10 +1480,10 @@
         <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>2.61567542300022</v>
+        <v>2.61572166037823</v>
       </c>
       <c r="H10" t="n">
-        <v>0.266309172716062</v>
+        <v>0.266328161330401</v>
       </c>
     </row>
     <row r="11">
@@ -1506,10 +1506,10 @@
         <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12221346618614</v>
+        <v>2.12151181288669</v>
       </c>
       <c r="H11" t="n">
-        <v>0.588657670421057</v>
+        <v>0.588465550326627</v>
       </c>
     </row>
     <row r="12">
@@ -1532,7 +1532,7 @@
         <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>2.06154741135949</v>
+        <v>2.06235109116948</v>
       </c>
       <c r="H12"/>
     </row>
@@ -1556,10 +1556,10 @@
         <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7609715488871</v>
+        <v>1.76041703797885</v>
       </c>
       <c r="H13" t="n">
-        <v>0.309479243177501</v>
+        <v>0.309379059161059</v>
       </c>
     </row>
     <row r="14">
@@ -1582,10 +1582,10 @@
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>1.72372903290371</v>
+        <v>1.72346055486539</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0811177032377772</v>
+        <v>0.0811025054272378</v>
       </c>
     </row>
     <row r="15">
@@ -1608,10 +1608,10 @@
         <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70582259717671</v>
+        <v>1.706495611628</v>
       </c>
       <c r="H15" t="n">
-        <v>1.05390239534565</v>
+        <v>1.05430225827595</v>
       </c>
     </row>
     <row r="16">
@@ -1634,10 +1634,10 @@
         <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>1.27604330034489</v>
+        <v>1.27570358577485</v>
       </c>
       <c r="H16" t="n">
-        <v>0.286174586870707</v>
+        <v>0.286113399427014</v>
       </c>
     </row>
     <row r="17">
@@ -1660,10 +1660,10 @@
         <v>107</v>
       </c>
       <c r="G17" t="n">
-        <v>0.98483464546458</v>
+        <v>0.984493672178256</v>
       </c>
       <c r="H17" t="n">
-        <v>0.41693837682382</v>
+        <v>0.416794022795259</v>
       </c>
     </row>
     <row r="18">
@@ -1686,10 +1686,10 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.749567042642019</v>
+        <v>0.749740683848614</v>
       </c>
       <c r="H18" t="n">
-        <v>0.194544793301194</v>
+        <v>0.194610471514287</v>
       </c>
     </row>
     <row r="19">
@@ -1712,7 +1712,7 @@
         <v>134</v>
       </c>
       <c r="G19" t="n">
-        <v>0.655033868085706</v>
+        <v>0.655082977305879</v>
       </c>
       <c r="H19"/>
     </row>
@@ -1736,10 +1736,10 @@
         <v>117</v>
       </c>
       <c r="G20" t="n">
-        <v>0.575423643279072</v>
+        <v>0.575654818115614</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0615288647184127</v>
+        <v>0.061570583041011</v>
       </c>
     </row>
     <row r="21">
@@ -1762,10 +1762,10 @@
         <v>83</v>
       </c>
       <c r="G21" t="n">
-        <v>0.564474994923797</v>
+        <v>0.564279560192745</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0340832466395912</v>
+        <v>0.0340714462052048</v>
       </c>
     </row>
     <row r="22">
@@ -1788,10 +1788,10 @@
         <v>137</v>
       </c>
       <c r="G22" t="n">
-        <v>0.476568415956346</v>
+        <v>0.476687591108285</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1140976927596</v>
+        <v>0.114127320086749</v>
       </c>
     </row>
     <row r="23">
@@ -1814,7 +1814,7 @@
         <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>0.374544787244193</v>
+        <v>0.374492362216465</v>
       </c>
       <c r="H23"/>
     </row>
@@ -1838,10 +1838,10 @@
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.346145091863355</v>
+        <v>0.346314940638425</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0399684363248702</v>
+        <v>0.0399880491030856</v>
       </c>
     </row>
     <row r="25">
@@ -1864,7 +1864,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="n">
-        <v>0.330421761971748</v>
+        <v>0.330467382668754</v>
       </c>
       <c r="H25"/>
     </row>
@@ -1888,10 +1888,10 @@
         <v>130</v>
       </c>
       <c r="G26" t="n">
-        <v>0.267395965692175</v>
+        <v>0.26736132531494</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0389345544674118</v>
+        <v>0.0389228832239507</v>
       </c>
     </row>
     <row r="27">
@@ -1914,10 +1914,10 @@
         <v>140</v>
       </c>
       <c r="G27" t="n">
-        <v>0.260992924556748</v>
+        <v>0.26104878829638</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00543901526738068</v>
+        <v>0.00544298482218474</v>
       </c>
     </row>
     <row r="28">
@@ -1940,7 +1940,7 @@
         <v>56</v>
       </c>
       <c r="G28" t="n">
-        <v>0.215379536261402</v>
+        <v>0.215484300157604</v>
       </c>
       <c r="H28"/>
     </row>
@@ -1964,7 +1964,7 @@
         <v>111</v>
       </c>
       <c r="G29" t="n">
-        <v>0.199995677947234</v>
+        <v>0.200091973222925</v>
       </c>
       <c r="H29"/>
     </row>
@@ -1988,10 +1988,10 @@
         <v>77</v>
       </c>
       <c r="G30" t="n">
-        <v>0.198168603278418</v>
+        <v>0.198099992572837</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0102348477225202</v>
+        <v>0.0102313041736828</v>
       </c>
     </row>
     <row r="31">
@@ -2014,10 +2014,10 @@
         <v>156</v>
       </c>
       <c r="G31" t="n">
-        <v>0.190073724118846</v>
+        <v>0.190090685332942</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00701588083467295</v>
+        <v>0.00707197848760562</v>
       </c>
     </row>
     <row r="32">
@@ -2040,7 +2040,7 @@
         <v>128</v>
       </c>
       <c r="G32" t="n">
-        <v>0.169225201387374</v>
+        <v>0.169310078329535</v>
       </c>
       <c r="H32"/>
     </row>
@@ -2064,7 +2064,7 @@
         <v>131</v>
       </c>
       <c r="G33" t="n">
-        <v>0.16153327223029</v>
+        <v>0.161612535374211</v>
       </c>
       <c r="H33"/>
     </row>
@@ -2088,7 +2088,7 @@
         <v>88</v>
       </c>
       <c r="G34" t="n">
-        <v>0.15404281807445</v>
+        <v>0.154072254049156</v>
       </c>
       <c r="H34"/>
     </row>
@@ -2112,10 +2112,10 @@
         <v>61</v>
       </c>
       <c r="G35" t="n">
-        <v>0.150868896821975</v>
+        <v>0.150844252164665</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0156795106512313</v>
+        <v>0.0156700114403627</v>
       </c>
     </row>
     <row r="36">
@@ -2138,7 +2138,7 @@
         <v>141</v>
       </c>
       <c r="G36" t="n">
-        <v>0.132112402185612</v>
+        <v>0.132066661715225</v>
       </c>
       <c r="H36"/>
     </row>
@@ -2162,7 +2162,7 @@
         <v>96</v>
       </c>
       <c r="G37" t="n">
-        <v>0.125162894608455</v>
+        <v>0.125138873055433</v>
       </c>
       <c r="H37"/>
     </row>
@@ -2186,10 +2186,10 @@
         <v>86</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0889305135628142</v>
+        <v>0.0889659391173463</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0193712470556227</v>
+        <v>0.0193723438294962</v>
       </c>
     </row>
     <row r="39">
@@ -2212,7 +2212,7 @@
         <v>147</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="H39"/>
     </row>
@@ -2236,7 +2236,7 @@
         <v>84</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="H40"/>
     </row>
@@ -2260,7 +2260,7 @@
         <v>159</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0230757874712522</v>
+        <v>0.0230871109140344</v>
       </c>
       <c r="H41"/>
     </row>
@@ -2284,7 +2284,7 @@
         <v>162</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0120112219919734</v>
+        <v>0.0120070634199185</v>
       </c>
       <c r="H42"/>
     </row>
@@ -2345,10 +2345,10 @@
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>19.4125027455314</v>
+        <v>19.4115818953403</v>
       </c>
       <c r="H2" t="n">
-        <v>1.41594364500501</v>
+        <v>1.4157656383204</v>
       </c>
     </row>
     <row r="3">
@@ -2371,10 +2371,10 @@
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>18.7585675464447</v>
+        <v>18.7596754229218</v>
       </c>
       <c r="H3" t="n">
-        <v>0.445227623743765</v>
+        <v>0.445256521377909</v>
       </c>
     </row>
     <row r="4">
@@ -2397,10 +2397,10 @@
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>15.4088131875933</v>
+        <v>15.4088719795948</v>
       </c>
       <c r="H4" t="n">
-        <v>10.7345361992899</v>
+        <v>10.7344944659556</v>
       </c>
     </row>
     <row r="5">
@@ -2423,10 +2423,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>8.27218139624052</v>
+        <v>8.27101045526418</v>
       </c>
       <c r="H5" t="n">
-        <v>1.36968109620548</v>
+        <v>1.36954730085311</v>
       </c>
     </row>
     <row r="6">
@@ -2449,10 +2449,10 @@
         <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>5.75200313986558</v>
+        <v>5.75290790518388</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01899653575214</v>
+        <v>1.01917258605361</v>
       </c>
     </row>
     <row r="7">
@@ -2475,10 +2475,10 @@
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>5.50235662250732</v>
+        <v>5.50252043016617</v>
       </c>
       <c r="H7" t="n">
-        <v>0.800444125543568</v>
+        <v>0.80046181295353</v>
       </c>
     </row>
     <row r="8">
@@ -2501,10 +2501,10 @@
         <v>107</v>
       </c>
       <c r="G8" t="n">
-        <v>4.01645242788765</v>
+        <v>4.01579072395459</v>
       </c>
       <c r="H8" t="n">
-        <v>1.90474767622298</v>
+        <v>1.90442337340355</v>
       </c>
     </row>
     <row r="9">
@@ -2527,10 +2527,10 @@
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79181291948954</v>
+        <v>3.79180493338407</v>
       </c>
       <c r="H9" t="n">
-        <v>0.523518167184392</v>
+        <v>0.523491402329329</v>
       </c>
     </row>
     <row r="10">
@@ -2553,10 +2553,10 @@
         <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>3.03219354452458</v>
+        <v>3.03231087200026</v>
       </c>
       <c r="H10" t="n">
-        <v>0.125337392344294</v>
+        <v>0.12535609475634</v>
       </c>
     </row>
     <row r="11">
@@ -2579,10 +2579,10 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.81823734043234</v>
+        <v>2.81821542032565</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0376989629613186</v>
+        <v>0.0376965176025091</v>
       </c>
     </row>
     <row r="12">
@@ -2605,10 +2605,10 @@
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>2.68256657067358</v>
+        <v>2.68243549456141</v>
       </c>
       <c r="H12" t="n">
-        <v>0.121381233006726</v>
+        <v>0.121368390366091</v>
       </c>
     </row>
     <row r="13">
@@ -2631,10 +2631,10 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>2.03818901815036</v>
+        <v>2.03841763438147</v>
       </c>
       <c r="H13" t="n">
-        <v>0.075051386182861</v>
+        <v>0.0750640111323821</v>
       </c>
     </row>
     <row r="14">
@@ -2657,10 +2657,10 @@
         <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73603927064758</v>
+        <v>1.73634246894241</v>
       </c>
       <c r="H14" t="n">
-        <v>0.137986526107818</v>
+        <v>0.138006835212184</v>
       </c>
     </row>
     <row r="15">
@@ -2683,10 +2683,10 @@
         <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>1.58574655495638</v>
+        <v>1.5857200763407</v>
       </c>
       <c r="H15" t="n">
-        <v>0.149916665967348</v>
+        <v>0.149933979851808</v>
       </c>
     </row>
     <row r="16">
@@ -2709,10 +2709,10 @@
         <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>1.10727470705888</v>
+        <v>1.10696295978783</v>
       </c>
       <c r="H16" t="n">
-        <v>0.554741443716215</v>
+        <v>0.554561864968259</v>
       </c>
     </row>
     <row r="17">
@@ -2735,10 +2735,10 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.619273063923512</v>
+        <v>0.619285054446558</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0899272762099066</v>
+        <v>0.0899205899723074</v>
       </c>
     </row>
     <row r="18">
@@ -2761,10 +2761,10 @@
         <v>77</v>
       </c>
       <c r="G18" t="n">
-        <v>0.533191579369875</v>
+        <v>0.533244440897158</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0473778828666499</v>
+        <v>0.0473843566599068</v>
       </c>
     </row>
     <row r="19">
@@ -2787,10 +2787,10 @@
         <v>87</v>
       </c>
       <c r="G19" t="n">
-        <v>0.421336013930581</v>
+        <v>0.421468998536732</v>
       </c>
       <c r="H19" t="n">
-        <v>0.208063181703773</v>
+        <v>0.208111513998807</v>
       </c>
     </row>
     <row r="20">
@@ -2813,10 +2813,10 @@
         <v>147</v>
       </c>
       <c r="G20" t="n">
-        <v>0.335446007240345</v>
+        <v>0.335502608919009</v>
       </c>
       <c r="H20" t="n">
-        <v>0.145391150819068</v>
+        <v>0.145399331381891</v>
       </c>
     </row>
     <row r="21">
@@ -2839,10 +2839,10 @@
         <v>61</v>
       </c>
       <c r="G21" t="n">
-        <v>0.327482849066667</v>
+        <v>0.327415679613048</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0352004257476803</v>
+        <v>0.035190434385075</v>
       </c>
     </row>
     <row r="22">
@@ -2865,10 +2865,10 @@
         <v>156</v>
       </c>
       <c r="G22" t="n">
-        <v>0.314411293591834</v>
+        <v>0.31444156830575</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0797749082016171</v>
+        <v>0.0797227487189153</v>
       </c>
     </row>
     <row r="23">
@@ -2891,10 +2891,10 @@
         <v>84</v>
       </c>
       <c r="G23" t="n">
-        <v>0.313011764481159</v>
+        <v>0.313003479629514</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0264669082796906</v>
+        <v>0.0264561600207882</v>
       </c>
     </row>
     <row r="24">
@@ -2917,10 +2917,10 @@
         <v>86</v>
       </c>
       <c r="G24" t="n">
-        <v>0.253850907049785</v>
+        <v>0.253812213615222</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07776340641984</v>
+        <v>0.0777507059732587</v>
       </c>
     </row>
     <row r="25">
@@ -2943,10 +2943,10 @@
         <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>0.247608728702917</v>
+        <v>0.247735129209194</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0422823286117328</v>
+        <v>0.0423031580187295</v>
       </c>
     </row>
     <row r="26">
@@ -2969,7 +2969,7 @@
         <v>141</v>
       </c>
       <c r="G26" t="n">
-        <v>0.152865481892164</v>
+        <v>0.152889701764647</v>
       </c>
       <c r="H26"/>
     </row>
@@ -2993,7 +2993,7 @@
         <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>0.152516179850445</v>
+        <v>0.152530179595588</v>
       </c>
       <c r="H27"/>
     </row>
@@ -3017,10 +3017,10 @@
         <v>130</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0980842454091233</v>
+        <v>0.0980799672171447</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0230756382404663</v>
+        <v>0.0230733844377137</v>
       </c>
     </row>
     <row r="29">
@@ -3043,7 +3043,7 @@
         <v>134</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0693347145734065</v>
+        <v>0.0693286314328213</v>
       </c>
       <c r="H29"/>
     </row>
@@ -3067,7 +3067,7 @@
         <v>157</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0437381858883574</v>
+        <v>0.0437387712383516</v>
       </c>
       <c r="H30"/>
     </row>
@@ -3091,7 +3091,7 @@
         <v>160</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0405851837376897</v>
+        <v>0.0405772956484978</v>
       </c>
       <c r="H31"/>
     </row>
@@ -3115,10 +3115,10 @@
         <v>111</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0249814785783675</v>
+        <v>0.0249786725070694</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00217042761827313</v>
+        <v>0.00216005472535743</v>
       </c>
     </row>
     <row r="33">
@@ -3141,10 +3141,10 @@
         <v>88</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0241030013505223</v>
+        <v>0.024115819301328</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00154925041334581</v>
+        <v>0.00154992537240909</v>
       </c>
     </row>
     <row r="34">
@@ -3167,7 +3167,7 @@
         <v>106</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0219120304044565</v>
+        <v>0.0219238938190009</v>
       </c>
       <c r="H34"/>
     </row>
@@ -3191,7 +3191,7 @@
         <v>36</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0197210594583907</v>
+        <v>0.0197308085877413</v>
       </c>
       <c r="H35"/>
     </row>
@@ -3215,7 +3215,7 @@
         <v>137</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0143747654178584</v>
+        <v>0.0143750880176955</v>
       </c>
       <c r="H36"/>
     </row>
@@ -3239,7 +3239,7 @@
         <v>56</v>
       </c>
       <c r="G37" t="n">
-        <v>0.013146986148294</v>
+        <v>0.0131538723918275</v>
       </c>
       <c r="H37"/>
     </row>
@@ -3263,10 +3263,10 @@
         <v>119</v>
       </c>
       <c r="G38" t="n">
-        <v>0.013146986148294</v>
+        <v>0.0131538723918275</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00309932140424106</v>
+        <v>0.00309985074481818</v>
       </c>
     </row>
     <row r="39">
@@ -3289,7 +3289,7 @@
         <v>162</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0112206027952913</v>
+        <v>0.0112136124278417</v>
       </c>
       <c r="H39"/>
     </row>
@@ -3313,7 +3313,7 @@
         <v>152</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00657407331009671</v>
+        <v>0.00657693619591377</v>
       </c>
       <c r="H40"/>
     </row>
@@ -3337,7 +3337,7 @@
         <v>105</v>
       </c>
       <c r="G41" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="H41"/>
     </row>
@@ -3361,7 +3361,7 @@
         <v>97</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="H42"/>
     </row>
@@ -3385,7 +3385,7 @@
         <v>93</v>
       </c>
       <c r="G43" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="H43"/>
     </row>
@@ -4541,10 +4541,10 @@
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>24.631392707249</v>
+        <v>24.6310091422731</v>
       </c>
       <c r="H2" t="n">
-        <v>4.59419934557097</v>
+        <v>4.59411313201896</v>
       </c>
     </row>
     <row r="3">
@@ -4567,10 +4567,10 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>21.9561628285138</v>
+        <v>21.9557849726509</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16771398525829</v>
+        <v>1.16769782773181</v>
       </c>
     </row>
     <row r="4">
@@ -4593,10 +4593,10 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>19.2655397706116</v>
+        <v>19.2658310749008</v>
       </c>
       <c r="H4" t="n">
-        <v>0.801037083083817</v>
+        <v>0.801053720061133</v>
       </c>
     </row>
     <row r="5">
@@ -4619,10 +4619,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>5.64193695488102</v>
+        <v>5.64180376429859</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11225319868185</v>
+        <v>1.11217301857517</v>
       </c>
     </row>
     <row r="6">
@@ -4645,10 +4645,10 @@
         <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54204949466641</v>
+        <v>5.5422000955275</v>
       </c>
       <c r="H6" t="n">
-        <v>1.05968322937623</v>
+        <v>1.05970997848961</v>
       </c>
     </row>
     <row r="7">
@@ -4671,10 +4671,10 @@
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>4.31468317592953</v>
+        <v>4.31466532273081</v>
       </c>
       <c r="H7" t="n">
-        <v>0.152549459352072</v>
+        <v>0.152541833505149</v>
       </c>
     </row>
     <row r="8">
@@ -4697,10 +4697,10 @@
         <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>3.93840198783546</v>
+        <v>3.93853124820496</v>
       </c>
       <c r="H8" t="n">
-        <v>2.37820589277897</v>
+        <v>2.37830413975467</v>
       </c>
     </row>
     <row r="9">
@@ -4723,10 +4723,10 @@
         <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68983581567514</v>
+        <v>2.68972901058529</v>
       </c>
       <c r="H9" t="n">
-        <v>0.324633621661211</v>
+        <v>0.324586081290426</v>
       </c>
     </row>
     <row r="10">
@@ -4749,10 +4749,10 @@
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.10025012562121</v>
+        <v>2.10056275535414</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0640374692467378</v>
+        <v>0.0640422498229953</v>
       </c>
     </row>
     <row r="11">
@@ -4775,10 +4775,10 @@
         <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>1.54109912852667</v>
+        <v>1.54123712106465</v>
       </c>
       <c r="H11" t="n">
-        <v>0.190189528807136</v>
+        <v>0.190209468161239</v>
       </c>
     </row>
     <row r="12">
@@ -4801,10 +4801,10 @@
         <v>147</v>
       </c>
       <c r="G12" t="n">
-        <v>1.14667551612367</v>
+        <v>1.1465334653637</v>
       </c>
       <c r="H12" t="n">
-        <v>0.369766800613695</v>
+        <v>0.36969012059224</v>
       </c>
     </row>
     <row r="13">
@@ -4827,10 +4827,10 @@
         <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>0.956395560811265</v>
+        <v>0.956500761814801</v>
       </c>
       <c r="H13" t="n">
-        <v>0.101961225414945</v>
+        <v>0.101967492441141</v>
       </c>
     </row>
     <row r="14">
@@ -4853,7 +4853,7 @@
         <v>162</v>
       </c>
       <c r="G14" t="n">
-        <v>0.82757160892989</v>
+        <v>0.827567995110726</v>
       </c>
       <c r="H14"/>
     </row>
@@ -4877,10 +4877,10 @@
         <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.74669543823414</v>
+        <v>0.74669857065911</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0292177805808028</v>
+        <v>0.0292161963875212</v>
       </c>
     </row>
     <row r="16">
@@ -4903,10 +4903,10 @@
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.70082866169531</v>
+        <v>0.700971005602779</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0239307351581613</v>
+        <v>0.0239368353304814</v>
       </c>
     </row>
     <row r="17">
@@ -4929,7 +4929,7 @@
         <v>165</v>
       </c>
       <c r="G17" t="n">
-        <v>0.561396773370258</v>
+        <v>0.561284058446422</v>
       </c>
       <c r="H17"/>
     </row>
@@ -4953,10 +4953,10 @@
         <v>107</v>
       </c>
       <c r="G18" t="n">
-        <v>0.509147384705421</v>
+        <v>0.509037052599851</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1146841955465</v>
+        <v>0.114665641911313</v>
       </c>
     </row>
     <row r="19">
@@ -4979,10 +4979,10 @@
         <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>0.494233263792842</v>
+        <v>0.494234140852321</v>
       </c>
       <c r="H19" t="n">
-        <v>0.212731530238071</v>
+        <v>0.212728315557499</v>
       </c>
     </row>
     <row r="20">
@@ -5005,10 +5005,10 @@
         <v>83</v>
       </c>
       <c r="G20" t="n">
-        <v>0.407956245260099</v>
+        <v>0.407987245009878</v>
       </c>
       <c r="H20" t="n">
-        <v>0.04072813612845</v>
+        <v>0.0407363638337707</v>
       </c>
     </row>
     <row r="21">
@@ -5031,10 +5031,10 @@
         <v>156</v>
       </c>
       <c r="G21" t="n">
-        <v>0.357665045351981</v>
+        <v>0.357642250946709</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0489665019883578</v>
+        <v>0.0489714570978644</v>
       </c>
     </row>
     <row r="22">
@@ -5057,10 +5057,10 @@
         <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>0.249306340048411</v>
+        <v>0.249311435523764</v>
       </c>
       <c r="H22" t="n">
-        <v>0.026880090038289</v>
+        <v>0.0268774857163241</v>
       </c>
     </row>
     <row r="23">
@@ -5083,7 +5083,7 @@
         <v>93</v>
       </c>
       <c r="G23" t="n">
-        <v>0.222556886622985</v>
+        <v>0.22251479576491</v>
       </c>
       <c r="H23"/>
     </row>
@@ -5107,10 +5107,10 @@
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>0.195206321884627</v>
+        <v>0.19522340424356</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0113929895460777</v>
+        <v>0.0113938240662738</v>
       </c>
     </row>
     <row r="25">
@@ -5133,10 +5133,10 @@
         <v>128</v>
       </c>
       <c r="G25" t="n">
-        <v>0.092479602397516</v>
+        <v>0.0924987590230735</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0146116242967509</v>
+        <v>0.014618736694941</v>
       </c>
     </row>
     <row r="26">
@@ -5159,10 +5159,10 @@
         <v>88</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0867179352064407</v>
+        <v>0.0867218270412637</v>
       </c>
       <c r="H26" t="n">
-        <v>0.03241140326452</v>
+        <v>0.0324165306828944</v>
       </c>
     </row>
     <row r="27">
@@ -5185,7 +5185,7 @@
         <v>105</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0794954454718848</v>
+        <v>0.0794804603356408</v>
       </c>
       <c r="H27"/>
     </row>
@@ -5209,10 +5209,10 @@
         <v>61</v>
       </c>
       <c r="G28" t="n">
-        <v>0.074254792274124</v>
+        <v>0.0742539301604906</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0189524110839475</v>
+        <v>0.0189479555191827</v>
       </c>
     </row>
     <row r="29">
@@ -5235,10 +5235,10 @@
         <v>66</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0571780437319009</v>
+        <v>0.0571686042728791</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0088145416049972</v>
+        <v>0.00880422534147926</v>
       </c>
     </row>
     <row r="30">
@@ -5261,10 +5261,10 @@
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0542304623700162</v>
+        <v>0.0542595553889274</v>
       </c>
       <c r="H30" t="n">
-        <v>0.011559847004357</v>
+        <v>0.0115623328292755</v>
       </c>
     </row>
     <row r="31">
@@ -5287,10 +5287,10 @@
         <v>86</v>
       </c>
       <c r="G31" t="n">
-        <v>0.051623866740213</v>
+        <v>0.0516379046782591</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0104755880492871</v>
+        <v>0.0104789957127142</v>
       </c>
     </row>
     <row r="32">
@@ -5313,10 +5313,10 @@
         <v>130</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0470087354670757</v>
+        <v>0.0470197133420486</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0132300081670565</v>
+        <v>0.0132324087357708</v>
       </c>
     </row>
     <row r="33">
@@ -5339,7 +5339,7 @@
         <v>101</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0461749605114494</v>
+        <v>0.046163617457175</v>
       </c>
       <c r="H33"/>
     </row>
@@ -5363,10 +5363,10 @@
         <v>87</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0389265345019701</v>
+        <v>0.0389413089858546</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0103389583512876</v>
+        <v>0.0103504220575672</v>
       </c>
     </row>
     <row r="35">
@@ -5389,7 +5389,7 @@
         <v>133</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0380134250583428</v>
+        <v>0.0380105048225147</v>
       </c>
       <c r="H35"/>
     </row>
@@ -5413,10 +5413,10 @@
         <v>99</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0330077239981236</v>
+        <v>0.033012673458996</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0187680021831362</v>
+        <v>0.0187745121440375</v>
       </c>
     </row>
     <row r="37">
@@ -5439,10 +5439,10 @@
         <v>56</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0319389969049558</v>
+        <v>0.0319286410918631</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0117066721670577</v>
+        <v>0.0116914178957773</v>
       </c>
     </row>
     <row r="38">
@@ -5465,7 +5465,7 @@
         <v>152</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0286275448625279</v>
+        <v>0.0286216562756727</v>
       </c>
       <c r="H38"/>
     </row>
@@ -5489,10 +5489,10 @@
         <v>122</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0282369750754459</v>
+        <v>0.0282420162483645</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00396353624307883</v>
+        <v>0.00397763717335705</v>
       </c>
     </row>
     <row r="40">
@@ -5515,7 +5515,7 @@
         <v>125</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0261506306073417</v>
+        <v>0.0261707673443559</v>
       </c>
       <c r="H40"/>
     </row>
@@ -5539,7 +5539,7 @@
         <v>157</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0215354993342044</v>
+        <v>0.0215518136787733</v>
       </c>
       <c r="H41"/>
     </row>
@@ -5563,10 +5563,10 @@
         <v>119</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0203103917598807</v>
+        <v>0.0203168400959636</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00385483829527122</v>
+        <v>0.00385801905830888</v>
       </c>
     </row>
     <row r="43">
@@ -5589,10 +5589,10 @@
         <v>104</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0191638558419427</v>
+        <v>0.0191573371209923</v>
       </c>
       <c r="H43" t="n">
-        <v>0.00702411118091624</v>
+        <v>0.00701517416642751</v>
       </c>
     </row>
     <row r="44">
@@ -5615,7 +5615,7 @@
         <v>74</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0169211308926826</v>
+        <v>0.0169336223425627</v>
       </c>
       <c r="H44"/>
     </row>
@@ -5639,10 +5639,10 @@
         <v>117</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0160080214490553</v>
+        <v>0.0160020558498507</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00446140558880036</v>
+        <v>0.00446170251848167</v>
       </c>
     </row>
     <row r="46">
@@ -5665,10 +5665,10 @@
         <v>137</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0140010114689522</v>
+        <v>0.0140070398830526</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00262057087127245</v>
+        <v>0.00262361767959266</v>
       </c>
     </row>
     <row r="47">
@@ -5691,7 +5691,7 @@
         <v>106</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0123059996195454</v>
+        <v>0.0123154310063522</v>
       </c>
       <c r="H47"/>
     </row>
@@ -5715,7 +5715,7 @@
         <v>167</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0107681310829099</v>
+        <v>0.0107762880040727</v>
       </c>
       <c r="H48"/>
     </row>
@@ -5739,7 +5739,7 @@
         <v>160</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0107681310829099</v>
+        <v>0.0107762880040727</v>
       </c>
       <c r="H49"/>
     </row>
@@ -5763,7 +5763,7 @@
         <v>168</v>
       </c>
       <c r="G50" t="n">
-        <v>0.00769163117802357</v>
+        <v>0.00769723967014162</v>
       </c>
       <c r="H50"/>
     </row>
@@ -5787,7 +5787,7 @@
         <v>141</v>
       </c>
       <c r="G51" t="n">
-        <v>0.00646576077208448</v>
+        <v>0.00646150375795982</v>
       </c>
       <c r="H51"/>
     </row>
@@ -5811,7 +5811,7 @@
         <v>169</v>
       </c>
       <c r="G52" t="n">
-        <v>0.00646576077208448</v>
+        <v>0.00646150375795982</v>
       </c>
       <c r="H52"/>
     </row>
@@ -5835,7 +5835,7 @@
         <v>159</v>
       </c>
       <c r="G53" t="n">
-        <v>0.00630938029092859</v>
+        <v>0.00630980021291098</v>
       </c>
       <c r="H53"/>
     </row>
@@ -5859,7 +5859,7 @@
         <v>129</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0061529998097727</v>
+        <v>0.00615809666786214</v>
       </c>
       <c r="H54"/>
     </row>
@@ -5883,7 +5883,7 @@
         <v>170</v>
       </c>
       <c r="G55" t="n">
-        <v>0.00484932057906336</v>
+        <v>0.00484612781846987</v>
       </c>
       <c r="H55"/>
     </row>
@@ -5907,7 +5907,7 @@
         <v>110</v>
       </c>
       <c r="G56" t="n">
-        <v>0.00461513127313722</v>
+        <v>0.00461819133621055</v>
       </c>
       <c r="H56"/>
     </row>
@@ -5931,7 +5931,7 @@
         <v>84</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00461513127313722</v>
+        <v>0.00461819133621055</v>
       </c>
       <c r="H57"/>
     </row>
@@ -5992,10 +5992,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>19.8741580235539</v>
+        <v>19.8722980417864</v>
       </c>
       <c r="H2" t="n">
-        <v>1.08247297210186</v>
+        <v>1.08232234927472</v>
       </c>
     </row>
     <row r="3">
@@ -6018,10 +6018,10 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>17.7241798195007</v>
+        <v>17.7224537820169</v>
       </c>
       <c r="H3" t="n">
-        <v>4.54736451659128</v>
+        <v>4.54672531155237</v>
       </c>
     </row>
     <row r="4">
@@ -6044,10 +6044,10 @@
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5118933543116</v>
+        <v>12.5158221148857</v>
       </c>
       <c r="H4" t="n">
-        <v>4.84513813620268</v>
+        <v>4.84664378215444</v>
       </c>
     </row>
     <row r="5">
@@ -6070,10 +6070,10 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>10.6290535606668</v>
+        <v>10.6283808772554</v>
       </c>
       <c r="H5" t="n">
-        <v>5.72148293638644</v>
+        <v>5.72085521364488</v>
       </c>
     </row>
     <row r="6">
@@ -6096,10 +6096,10 @@
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>9.39450066973325</v>
+        <v>9.39293921525338</v>
       </c>
       <c r="H6" t="n">
-        <v>1.66634977712536</v>
+        <v>1.6659702542067</v>
       </c>
     </row>
     <row r="7">
@@ -6122,10 +6122,10 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>6.00404627902126</v>
+        <v>6.00307210922042</v>
       </c>
       <c r="H7" t="n">
-        <v>1.24378836207599</v>
+        <v>1.24351144922079</v>
       </c>
     </row>
     <row r="8">
@@ -6148,10 +6148,10 @@
         <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84999160049945</v>
+        <v>5.84984507449901</v>
       </c>
       <c r="H8" t="n">
-        <v>0.802981898007005</v>
+        <v>0.802960025767448</v>
       </c>
     </row>
     <row r="9">
@@ -6174,7 +6174,7 @@
         <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>5.12700882116796</v>
+        <v>5.12663012137111</v>
       </c>
       <c r="H9"/>
     </row>
@@ -6198,10 +6198,10 @@
         <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5410657193669</v>
+        <v>4.54254025821407</v>
       </c>
       <c r="H10" t="n">
-        <v>1.26372211027965</v>
+        <v>1.26424553476954</v>
       </c>
     </row>
     <row r="11">
@@ -6224,10 +6224,10 @@
         <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>3.42924529730402</v>
+        <v>3.4306325226418</v>
       </c>
       <c r="H11" t="n">
-        <v>1.30875082780457</v>
+        <v>1.30926703969254</v>
       </c>
     </row>
     <row r="12">
@@ -6250,10 +6250,10 @@
         <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>1.21751116830729</v>
+        <v>1.2177090508129</v>
       </c>
       <c r="H12" t="n">
-        <v>0.489497778370004</v>
+        <v>0.489615016945174</v>
       </c>
     </row>
     <row r="13">
@@ -6276,10 +6276,10 @@
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>1.08354447878472</v>
+        <v>1.0837060721082</v>
       </c>
       <c r="H13" t="n">
-        <v>0.269216117329756</v>
+        <v>0.269245368434525</v>
       </c>
     </row>
     <row r="14">
@@ -6302,10 +6302,10 @@
         <v>54</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0764610187463</v>
+        <v>1.07669850745551</v>
       </c>
       <c r="H14" t="n">
-        <v>0.186974950143159</v>
+        <v>0.18702418051521</v>
       </c>
     </row>
     <row r="15">
@@ -6328,10 +6328,10 @@
         <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.776644275718104</v>
+        <v>0.776524088548015</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0412337211331349</v>
+        <v>0.0411156528901548</v>
       </c>
     </row>
     <row r="16">
@@ -6354,10 +6354,10 @@
         <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>0.272068552038335</v>
+        <v>0.272095187481516</v>
       </c>
       <c r="H16" t="n">
-        <v>0.112442581800846</v>
+        <v>0.112472967401727</v>
       </c>
     </row>
     <row r="17">
@@ -6380,7 +6380,7 @@
         <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>0.106510209713172</v>
+        <v>0.106529229357992</v>
       </c>
       <c r="H17"/>
     </row>
@@ -6404,10 +6404,10 @@
         <v>66</v>
       </c>
       <c r="G18" t="n">
-        <v>0.077869070758711</v>
+        <v>0.0778868105568116</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0128911473218381</v>
+        <v>0.0129181946812718</v>
       </c>
     </row>
     <row r="19">
@@ -6430,7 +6430,7 @@
         <v>69</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0745489076284746</v>
+        <v>0.0745232685650044</v>
       </c>
       <c r="H19"/>
     </row>
@@ -6454,7 +6454,7 @@
         <v>71</v>
       </c>
       <c r="G20" t="n">
-        <v>0.048049953067902</v>
+        <v>0.0480779483382211</v>
       </c>
       <c r="H20"/>
     </row>
@@ -6478,7 +6478,7 @@
         <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0447297899376656</v>
+        <v>0.0447144063464139</v>
       </c>
       <c r="H21"/>
     </row>
@@ -6502,7 +6502,7 @@
         <v>73</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0372744538142373</v>
+        <v>0.0372616342825022</v>
       </c>
       <c r="H22"/>
     </row>
@@ -6526,7 +6526,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="n">
-        <v>0.034321713163202</v>
+        <v>0.0343410736648642</v>
       </c>
       <c r="H23"/>
     </row>
@@ -6550,7 +6550,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="n">
-        <v>0.029819117690809</v>
+        <v>0.0298088622185905</v>
       </c>
       <c r="H24"/>
     </row>
@@ -6574,7 +6574,7 @@
         <v>77</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0205934732585021</v>
+        <v>0.0206041989915073</v>
       </c>
       <c r="H25"/>
     </row>
@@ -6598,7 +6598,7 @@
         <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0149106722468566</v>
+        <v>0.0149055441278233</v>
       </c>
       <c r="H26"/>
     </row>
@@ -6659,10 +6659,10 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>56.2950113123006</v>
+        <v>56.3041081219849</v>
       </c>
       <c r="H2" t="n">
-        <v>13.8490255669441</v>
+        <v>13.856182263946</v>
       </c>
     </row>
     <row r="3">
@@ -6685,10 +6685,10 @@
         <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>17.0508572343531</v>
+        <v>17.0352886501756</v>
       </c>
       <c r="H3" t="n">
-        <v>4.68457221441722</v>
+        <v>4.67777158284229</v>
       </c>
     </row>
     <row r="4">
@@ -6711,10 +6711,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>8.97414045002143</v>
+        <v>8.97376302770651</v>
       </c>
       <c r="H4" t="n">
-        <v>2.23722456511995</v>
+        <v>2.23691437036538</v>
       </c>
     </row>
     <row r="5">
@@ -6737,10 +6737,10 @@
         <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>4.65985259507985</v>
+        <v>4.66228845333324</v>
       </c>
       <c r="H5" t="n">
-        <v>3.20270178727532</v>
+        <v>3.20458350215252</v>
       </c>
     </row>
     <row r="6">
@@ -6763,10 +6763,10 @@
         <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.95563362159775</v>
+        <v>2.95631754482207</v>
       </c>
       <c r="H6" t="n">
-        <v>0.166350486782069</v>
+        <v>0.166443705551338</v>
       </c>
     </row>
     <row r="7">
@@ -6789,10 +6789,10 @@
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>2.06278940323585</v>
+        <v>2.06322419020452</v>
       </c>
       <c r="H7" t="n">
-        <v>0.443730531241504</v>
+        <v>0.443716737739581</v>
       </c>
     </row>
     <row r="8">
@@ -6815,10 +6815,10 @@
         <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98068645471414</v>
+        <v>1.98260103785225</v>
       </c>
       <c r="H8" t="n">
-        <v>0.40990712214849</v>
+        <v>0.410246235998562</v>
       </c>
     </row>
     <row r="9">
@@ -6841,10 +6841,10 @@
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>1.36113341054947</v>
+        <v>1.36142375061603</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0687858803288349</v>
+        <v>0.0688214454572211</v>
       </c>
     </row>
     <row r="10">
@@ -6867,10 +6867,10 @@
         <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>0.967041921835672</v>
+        <v>0.967424695406141</v>
       </c>
       <c r="H10" t="n">
-        <v>0.137633057761389</v>
+        <v>0.137743280417042</v>
       </c>
     </row>
     <row r="11">
@@ -6893,10 +6893,10 @@
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.783710097716881</v>
+        <v>0.783743056997747</v>
       </c>
       <c r="H11" t="n">
-        <v>0.064833146768481</v>
+        <v>0.0648284348756534</v>
       </c>
     </row>
     <row r="12">
@@ -6919,10 +6919,10 @@
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.782625180169578</v>
+        <v>0.782826515834002</v>
       </c>
       <c r="H12" t="n">
-        <v>0.265920244800812</v>
+        <v>0.265934164649738</v>
       </c>
     </row>
     <row r="13">
@@ -6945,10 +6945,10 @@
         <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>0.653944782403579</v>
+        <v>0.653790508001574</v>
       </c>
       <c r="H13" t="n">
-        <v>0.133944302900671</v>
+        <v>0.133970579529824</v>
       </c>
     </row>
     <row r="14">
@@ -6971,10 +6971,10 @@
         <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>0.42055134000046</v>
+        <v>0.420978721028352</v>
       </c>
       <c r="H14" t="n">
-        <v>0.251217866740883</v>
+        <v>0.251600768850808</v>
       </c>
     </row>
     <row r="15">
@@ -6997,10 +6997,10 @@
         <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>0.294797111390009</v>
+        <v>0.294801554152728</v>
       </c>
       <c r="H15" t="n">
-        <v>0.060127286461208</v>
+        <v>0.0601038972054638</v>
       </c>
     </row>
     <row r="16">
@@ -7023,7 +7023,7 @@
         <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>0.273245290917606</v>
+        <v>0.273220773321349</v>
       </c>
       <c r="H16"/>
     </row>
@@ -7047,10 +7047,10 @@
         <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>0.110220518298119</v>
+        <v>0.110260935136766</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0450243073135336</v>
+        <v>0.0450239683206631</v>
       </c>
     </row>
     <row r="18">
@@ -7073,7 +7073,7 @@
         <v>85</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0949843092504629</v>
+        <v>0.0948848870789554</v>
       </c>
       <c r="H18"/>
     </row>
@@ -7097,10 +7097,10 @@
         <v>77</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0905129096455505</v>
+        <v>0.0906268818335357</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0213347951269941</v>
+        <v>0.0213609609007617</v>
       </c>
     </row>
     <row r="20">
@@ -7123,7 +7123,7 @@
         <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>0.051722296985655</v>
+        <v>0.0517867896191633</v>
       </c>
       <c r="H20"/>
     </row>
@@ -7147,7 +7147,7 @@
         <v>86</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0374081938479166</v>
+        <v>0.0373818914578821</v>
       </c>
       <c r="H21"/>
     </row>
@@ -7171,10 +7171,10 @@
         <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>0.030170476513252</v>
+        <v>0.0302089606111786</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00304767836202143</v>
+        <v>0.00305156584296595</v>
       </c>
     </row>
     <row r="23">
@@ -7197,7 +7197,7 @@
         <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0215503403666086</v>
+        <v>0.0215778290079847</v>
       </c>
       <c r="H23"/>
     </row>
@@ -7221,7 +7221,7 @@
         <v>88</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0172402722932869</v>
+        <v>0.0172622632063878</v>
       </c>
       <c r="H24"/>
     </row>
@@ -7245,7 +7245,7 @@
         <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0172402722932869</v>
+        <v>0.0172622632063878</v>
       </c>
       <c r="H25"/>
     </row>
@@ -7269,7 +7269,7 @@
         <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0129302042199652</v>
+        <v>0.0129466974047908</v>
       </c>
       <c r="H26"/>
     </row>
@@ -7330,10 +7330,10 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>39.7281014519403</v>
+        <v>39.7290616830707</v>
       </c>
       <c r="H2" t="n">
-        <v>6.21860820764229</v>
+        <v>6.21835232915755</v>
       </c>
     </row>
     <row r="3">
@@ -7356,10 +7356,10 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>34.8879985888077</v>
+        <v>34.8859603682263</v>
       </c>
       <c r="H3" t="n">
-        <v>4.42073812416722</v>
+        <v>4.42043960561398</v>
       </c>
     </row>
     <row r="4">
@@ -7382,10 +7382,10 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>7.53251208659025</v>
+        <v>7.53238581525108</v>
       </c>
       <c r="H4" t="n">
-        <v>0.237454364070223</v>
+        <v>0.237447338734724</v>
       </c>
     </row>
     <row r="5">
@@ -7408,10 +7408,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>4.44575576170417</v>
+        <v>4.44623453436161</v>
       </c>
       <c r="H5" t="n">
-        <v>0.630523071027679</v>
+        <v>0.63055259443331</v>
       </c>
     </row>
     <row r="6">
@@ -7434,10 +7434,10 @@
         <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>3.87693343243817</v>
+        <v>3.87731620473622</v>
       </c>
       <c r="H6" t="n">
-        <v>0.911712337636597</v>
+        <v>0.911805512809434</v>
       </c>
     </row>
     <row r="7">
@@ -7460,10 +7460,10 @@
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25694228270683</v>
+        <v>3.25710668864576</v>
       </c>
       <c r="H7" t="n">
-        <v>0.70733559831466</v>
+        <v>0.707350658262006</v>
       </c>
     </row>
     <row r="8">
@@ -7486,10 +7486,10 @@
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97872409787126</v>
+        <v>1.97872599818862</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1547972235296</v>
+        <v>0.154806328395301</v>
       </c>
     </row>
     <row r="9">
@@ -7512,7 +7512,7 @@
         <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>1.12314048822747</v>
+        <v>1.12319999181149</v>
       </c>
       <c r="H9"/>
     </row>
@@ -7536,7 +7536,7 @@
         <v>93</v>
       </c>
       <c r="G10" t="n">
-        <v>0.918428526744664</v>
+        <v>0.918331540824173</v>
       </c>
       <c r="H10"/>
     </row>
@@ -7560,10 +7560,10 @@
         <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.558108885552207</v>
+        <v>0.558162676090998</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0461198226177086</v>
+        <v>0.0461237017220785</v>
       </c>
     </row>
     <row r="12">
@@ -7586,10 +7586,10 @@
         <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>0.494833544322251</v>
+        <v>0.494917936870067</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0431730031535043</v>
+        <v>0.043185765399925</v>
       </c>
     </row>
     <row r="13">
@@ -7612,10 +7612,10 @@
         <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2535018465008</v>
+        <v>0.253525157028426</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0546702359334213</v>
+        <v>0.0546684509143556</v>
       </c>
     </row>
     <row r="14">
@@ -7638,10 +7638,10 @@
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.149049513109839</v>
+        <v>0.149076724973757</v>
       </c>
       <c r="H14" t="n">
-        <v>0.022773446583883</v>
+        <v>0.0227812590279868</v>
       </c>
     </row>
     <row r="15">
@@ -7664,10 +7664,10 @@
         <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>0.108401006922979</v>
+        <v>0.108387807070915</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0395979660187865</v>
+        <v>0.0395979486402563</v>
       </c>
     </row>
     <row r="16">
@@ -7690,10 +7690,10 @@
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0983739961246108</v>
+        <v>0.0984050641522545</v>
       </c>
       <c r="H16" t="n">
-        <v>0.021972442960277</v>
+        <v>0.0219792946428027</v>
       </c>
     </row>
     <row r="17">
@@ -7716,10 +7716,10 @@
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0862854408888624</v>
+        <v>0.0863011193017688</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0119456540453731</v>
+        <v>0.0119485130265267</v>
       </c>
     </row>
     <row r="18">
@@ -7742,7 +7742,7 @@
         <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0846707889820255</v>
+        <v>0.0846647635257898</v>
       </c>
       <c r="H18"/>
     </row>
@@ -7766,7 +7766,7 @@
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0603012976389215</v>
+        <v>0.0603064817301813</v>
       </c>
       <c r="H19"/>
     </row>
@@ -7790,7 +7790,7 @@
         <v>97</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0567665798345247</v>
+        <v>0.056760670105872</v>
       </c>
       <c r="H20"/>
     </row>
@@ -7814,10 +7814,10 @@
         <v>83</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0500354950193752</v>
+        <v>0.0500356743516428</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0267642568796029</v>
+        <v>0.0267683469819272</v>
       </c>
     </row>
     <row r="22">
@@ -7840,10 +7840,10 @@
         <v>61</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0376415257929039</v>
+        <v>0.0376593776481822</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0129554095710758</v>
+        <v>0.0129613740499146</v>
       </c>
     </row>
     <row r="23">
@@ -7866,10 +7866,10 @@
         <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0290869397978496</v>
+        <v>0.0291004962026295</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0157285794869354</v>
+        <v>0.0157351004563593</v>
       </c>
     </row>
     <row r="24">
@@ -7892,10 +7892,10 @@
         <v>99</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0268330144888622</v>
+        <v>0.0268281539567913</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00748556523992058</v>
+        <v>0.00748741271841554</v>
       </c>
     </row>
     <row r="25">
@@ -7918,7 +7918,7 @@
         <v>101</v>
       </c>
       <c r="G25" t="n">
-        <v>0.026401093232374</v>
+        <v>0.0263889491829003</v>
       </c>
       <c r="H25"/>
     </row>
@@ -7942,7 +7942,7 @@
         <v>104</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0222428218635845</v>
+        <v>0.0222527924706864</v>
       </c>
       <c r="H26"/>
     </row>
@@ -7966,7 +7966,7 @@
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.016358362596248</v>
+        <v>0.0163605648822847</v>
       </c>
       <c r="H27"/>
     </row>
@@ -7990,7 +7990,7 @@
         <v>73</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0162468266045379</v>
+        <v>0.0162393533433233</v>
       </c>
       <c r="H28"/>
     </row>
@@ -8014,7 +8014,7 @@
         <v>88</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0142159732789706</v>
+        <v>0.0142094341754078</v>
       </c>
       <c r="H29"/>
     </row>
@@ -8038,7 +8038,7 @@
         <v>87</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0121851199534034</v>
+        <v>0.0121795150074924</v>
       </c>
       <c r="H30"/>
     </row>
@@ -8062,7 +8062,7 @@
         <v>105</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0121851199534034</v>
+        <v>0.0121795150074924</v>
       </c>
       <c r="H31"/>
     </row>
@@ -8086,7 +8086,7 @@
         <v>106</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00812341330226893</v>
+        <v>0.00811967667166163</v>
       </c>
       <c r="H32"/>
     </row>
@@ -8110,7 +8110,7 @@
         <v>85</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00812341330226893</v>
+        <v>0.00811967667166163</v>
       </c>
       <c r="H33"/>
     </row>
@@ -8134,7 +8134,7 @@
         <v>66</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0068441179342651</v>
+        <v>0.00684695551256686</v>
       </c>
       <c r="H34"/>
     </row>
@@ -8158,7 +8158,7 @@
         <v>107</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0060925599767017</v>
+        <v>0.00608975750374622</v>
       </c>
       <c r="H35"/>
     </row>
@@ -8182,7 +8182,7 @@
         <v>36</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00513290130977313</v>
+        <v>0.00513502957958107</v>
       </c>
       <c r="H36"/>
     </row>
@@ -8206,7 +8206,7 @@
         <v>108</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00342168468528117</v>
+        <v>0.00342385186597158</v>
       </c>
       <c r="H37"/>
     </row>
@@ -9208,10 +9208,10 @@
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>15.9046629771807</v>
+        <v>15.9133360695454</v>
       </c>
       <c r="H2" t="n">
-        <v>1.08475902120531</v>
+        <v>1.0856805763707</v>
       </c>
     </row>
     <row r="3">
@@ -9234,10 +9234,10 @@
         <v>112</v>
       </c>
       <c r="G3" t="n">
-        <v>11.4997988322463</v>
+        <v>11.4962127695466</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83502063905079</v>
+        <v>1.8347445177039</v>
       </c>
     </row>
     <row r="4">
@@ -9260,10 +9260,10 @@
         <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>11.2813693050418</v>
+        <v>11.2805137349966</v>
       </c>
       <c r="H4" t="n">
-        <v>0.902135180565654</v>
+        <v>0.901845088166167</v>
       </c>
     </row>
     <row r="5">
@@ -9286,10 +9286,10 @@
         <v>111</v>
       </c>
       <c r="G5" t="n">
-        <v>9.04064253626956</v>
+        <v>9.04007656688433</v>
       </c>
       <c r="H5" t="n">
-        <v>1.22878413366926</v>
+        <v>1.22890237664976</v>
       </c>
     </row>
     <row r="6">
@@ -9312,10 +9312,10 @@
         <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>8.11880458079717</v>
+        <v>8.1187833078828</v>
       </c>
       <c r="H6" t="n">
-        <v>0.597163209200319</v>
+        <v>0.597374451018991</v>
       </c>
     </row>
     <row r="7">
@@ -9338,10 +9338,10 @@
         <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>7.26546809884088</v>
+        <v>7.26449224855581</v>
       </c>
       <c r="H7" t="n">
-        <v>0.509778166469935</v>
+        <v>0.509542697259636</v>
       </c>
     </row>
     <row r="8">
@@ -9364,10 +9364,10 @@
         <v>66</v>
       </c>
       <c r="G8" t="n">
-        <v>5.88840392521765</v>
+        <v>5.88727823712654</v>
       </c>
       <c r="H8" t="n">
-        <v>0.590100815130695</v>
+        <v>0.590136456318376</v>
       </c>
     </row>
     <row r="9">
@@ -9390,10 +9390,10 @@
         <v>110</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44997202434239</v>
+        <v>4.44837417124006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.965439863915427</v>
+        <v>0.965417078288699</v>
       </c>
     </row>
     <row r="10">
@@ -9416,10 +9416,10 @@
         <v>121</v>
       </c>
       <c r="G10" t="n">
-        <v>3.50914346504936</v>
+        <v>3.50962344380878</v>
       </c>
       <c r="H10" t="n">
-        <v>0.207091168383744</v>
+        <v>0.207271608753574</v>
       </c>
     </row>
     <row r="11">
@@ -9442,10 +9442,10 @@
         <v>117</v>
       </c>
       <c r="G11" t="n">
-        <v>3.43804653531843</v>
+        <v>3.43986679846598</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0946539325824996</v>
+        <v>0.0947048533378927</v>
       </c>
     </row>
     <row r="12">
@@ -9468,10 +9468,10 @@
         <v>119</v>
       </c>
       <c r="G12" t="n">
-        <v>2.64075687429571</v>
+        <v>2.6415769192628</v>
       </c>
       <c r="H12" t="n">
-        <v>0.595101776309266</v>
+        <v>0.595357459589207</v>
       </c>
     </row>
     <row r="13">
@@ -9494,10 +9494,10 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>2.43688047244979</v>
+        <v>2.43792174692203</v>
       </c>
       <c r="H13" t="n">
-        <v>0.244277250081718</v>
+        <v>0.244464437518885</v>
       </c>
     </row>
     <row r="14">
@@ -9520,10 +9520,10 @@
         <v>122</v>
       </c>
       <c r="G14" t="n">
-        <v>1.84799400726404</v>
+        <v>1.84783337527055</v>
       </c>
       <c r="H14" t="n">
-        <v>0.249230689888784</v>
+        <v>0.249197462551498</v>
       </c>
     </row>
     <row r="15">
@@ -9546,10 +9546,10 @@
         <v>118</v>
       </c>
       <c r="G15" t="n">
-        <v>1.66033677490238</v>
+        <v>1.6606175322496</v>
       </c>
       <c r="H15" t="n">
-        <v>1.13579060248245</v>
+        <v>1.13593148240188</v>
       </c>
     </row>
     <row r="16">
@@ -9572,10 +9572,10 @@
         <v>75</v>
       </c>
       <c r="G16" t="n">
-        <v>1.31606078298467</v>
+        <v>1.31604890737969</v>
       </c>
       <c r="H16" t="n">
-        <v>0.361395917771337</v>
+        <v>0.36116100920028</v>
       </c>
     </row>
     <row r="17">
@@ -9598,10 +9598,10 @@
         <v>134</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25747421750289</v>
+        <v>1.25638189709843</v>
       </c>
       <c r="H17" t="n">
-        <v>0.253631704218556</v>
+        <v>0.254132630138318</v>
       </c>
     </row>
     <row r="18">
@@ -9624,10 +9624,10 @@
         <v>128</v>
       </c>
       <c r="G18" t="n">
-        <v>1.07670400831027</v>
+        <v>1.07711794991603</v>
       </c>
       <c r="H18" t="n">
-        <v>0.298241259617882</v>
+        <v>0.298351762732855</v>
       </c>
     </row>
     <row r="19">
@@ -9650,10 +9650,10 @@
         <v>125</v>
       </c>
       <c r="G19" t="n">
-        <v>0.87912479341694</v>
+        <v>0.879560142730045</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14776043556623</v>
+        <v>0.147758199768971</v>
       </c>
     </row>
     <row r="20">
@@ -9676,10 +9676,10 @@
         <v>101</v>
       </c>
       <c r="G20" t="n">
-        <v>0.826099667163471</v>
+        <v>0.824933538631586</v>
       </c>
       <c r="H20" t="n">
-        <v>0.172201923099766</v>
+        <v>0.171922117135325</v>
       </c>
     </row>
     <row r="21">
@@ -9702,10 +9702,10 @@
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.74281337850058</v>
+        <v>0.741563473474212</v>
       </c>
       <c r="H21" t="n">
-        <v>0.49049152785471</v>
+        <v>0.489687992578949</v>
       </c>
     </row>
     <row r="22">
@@ -9728,10 +9728,10 @@
         <v>123</v>
       </c>
       <c r="G22" t="n">
-        <v>0.693226457958619</v>
+        <v>0.692893953665318</v>
       </c>
       <c r="H22" t="n">
-        <v>0.32670105585919</v>
+        <v>0.326398657182892</v>
       </c>
     </row>
     <row r="23">
@@ -9754,10 +9754,10 @@
         <v>130</v>
       </c>
       <c r="G23" t="n">
-        <v>0.547062921171909</v>
+        <v>0.547646792897094</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0909057071915145</v>
+        <v>0.0909623774484016</v>
       </c>
     </row>
     <row r="24">
@@ -9780,10 +9780,10 @@
         <v>127</v>
       </c>
       <c r="G24" t="n">
-        <v>0.419796251115969</v>
+        <v>0.419715937423794</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0794751912347708</v>
+        <v>0.0793898603845195</v>
       </c>
     </row>
     <row r="25">
@@ -9806,10 +9806,10 @@
         <v>133</v>
       </c>
       <c r="G25" t="n">
-        <v>0.408857309590412</v>
+        <v>0.408906370374657</v>
       </c>
       <c r="H25" t="n">
-        <v>0.089609232738448</v>
+        <v>0.0895754778806432</v>
       </c>
     </row>
     <row r="26">
@@ -9832,10 +9832,10 @@
         <v>131</v>
       </c>
       <c r="G26" t="n">
-        <v>0.359219098942673</v>
+        <v>0.359167539819473</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0238016846565754</v>
+        <v>0.0237482075559623</v>
       </c>
     </row>
     <row r="27">
@@ -9858,10 +9858,10 @@
         <v>124</v>
       </c>
       <c r="G27" t="n">
-        <v>0.312281577657832</v>
+        <v>0.312328729415327</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0582763759092555</v>
+        <v>0.0580625396139329</v>
       </c>
     </row>
     <row r="28">
@@ -9884,10 +9884,10 @@
         <v>54</v>
       </c>
       <c r="G28" t="n">
-        <v>0.298005242007987</v>
+        <v>0.297697170490835</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0245469511332483</v>
+        <v>0.0245026224151622</v>
       </c>
     </row>
     <row r="29">
@@ -9910,7 +9910,7 @@
         <v>132</v>
       </c>
       <c r="G29" t="n">
-        <v>0.251395800537696</v>
+        <v>0.251333021127533</v>
       </c>
       <c r="H29"/>
     </row>
@@ -9934,7 +9934,7 @@
         <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.219769260139959</v>
+        <v>0.219623369698133</v>
       </c>
       <c r="H30"/>
     </row>
@@ -9958,10 +9958,10 @@
         <v>126</v>
       </c>
       <c r="G31" t="n">
-        <v>0.21788302228434</v>
+        <v>0.217897650374912</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0871378672283708</v>
+        <v>0.0870470200100146</v>
       </c>
     </row>
     <row r="32">
@@ -9984,7 +9984,7 @@
         <v>28</v>
       </c>
       <c r="G32" t="n">
-        <v>0.206343632796305</v>
+        <v>0.206220812316201</v>
       </c>
       <c r="H32"/>
     </row>
@@ -10008,10 +10008,10 @@
         <v>137</v>
       </c>
       <c r="G33" t="n">
-        <v>0.138580559940982</v>
+        <v>0.138286935951815</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0884303688003574</v>
+        <v>0.0882073973999568</v>
       </c>
     </row>
     <row r="34">
@@ -10034,10 +10034,10 @@
         <v>135</v>
       </c>
       <c r="G34" t="n">
-        <v>0.127680528150844</v>
+        <v>0.127532069617423</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0239303508272499</v>
+        <v>0.0239786372902238</v>
       </c>
     </row>
     <row r="35">
@@ -10060,7 +10060,7 @@
         <v>138</v>
       </c>
       <c r="G35" t="n">
-        <v>0.114468904351991</v>
+        <v>0.114437424323326</v>
       </c>
       <c r="H35"/>
     </row>
@@ -10084,10 +10084,10 @@
         <v>106</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0850947070476735</v>
+        <v>0.0849846185119218</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0283005944105174</v>
+        <v>0.0281740877995576</v>
       </c>
     </row>
     <row r="37">
@@ -10110,7 +10110,7 @@
         <v>139</v>
       </c>
       <c r="G37" t="n">
-        <v>0.083112079165677</v>
+        <v>0.083118618323469</v>
       </c>
       <c r="H37"/>
     </row>
@@ -10134,10 +10134,10 @@
         <v>140</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0826672701448722</v>
+        <v>0.0824763260600204</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00157951570916209</v>
+        <v>0.00157586735859885</v>
       </c>
     </row>
     <row r="39">
@@ -10160,7 +10160,7 @@
         <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>0.081013606389594</v>
+        <v>0.0810849869124129</v>
       </c>
       <c r="H39"/>
     </row>
@@ -10184,10 +10184,10 @@
         <v>19</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0625588957431237</v>
+        <v>0.0624143977927732</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00844884085840169</v>
+        <v>0.00842932580506875</v>
       </c>
     </row>
     <row r="41">
@@ -10210,10 +10210,10 @@
         <v>17</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0491536075793476</v>
+        <v>0.049040073037806</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0123053091295971</v>
+        <v>0.0122768864420395</v>
       </c>
     </row>
     <row r="42">
@@ -10236,10 +10236,10 @@
         <v>141</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0447621133500903</v>
+        <v>0.044693130754824</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0189029136531948</v>
+        <v>0.0188349213869587</v>
       </c>
     </row>
     <row r="43">
@@ -10262,10 +10262,10 @@
         <v>27</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0268689409306797</v>
+        <v>0.0268333473908288</v>
       </c>
       <c r="H43" t="n">
-        <v>0.00943832546084426</v>
+        <v>0.00939780914090776</v>
       </c>
     </row>
     <row r="44">
@@ -10288,10 +10288,10 @@
         <v>20</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0245768037896738</v>
+        <v>0.024520036518903</v>
       </c>
       <c r="H44" t="n">
-        <v>0.011059111176659</v>
+        <v>0.0110335669454391</v>
       </c>
     </row>
     <row r="45">
@@ -10314,10 +10314,10 @@
         <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0224394212781726</v>
+        <v>0.02243082212351</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0000681580412900505</v>
+        <v>0.0000985696922639011</v>
       </c>
     </row>
     <row r="46">
@@ -10340,7 +10340,7 @@
         <v>73</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0178737175517015</v>
+        <v>0.017832433006623</v>
       </c>
       <c r="H46"/>
     </row>
@@ -10364,7 +10364,7 @@
         <v>85</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0157752447756186</v>
+        <v>0.0157988015955669</v>
       </c>
       <c r="H47"/>
     </row>
@@ -10388,7 +10388,7 @@
         <v>42</v>
       </c>
       <c r="G48" t="n">
-        <v>0.00450733912334368</v>
+        <v>0.00451369123599265</v>
       </c>
       <c r="H48"/>
     </row>
@@ -10412,7 +10412,7 @@
         <v>18</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00446842938792537</v>
+        <v>0.00445810825165575</v>
       </c>
       <c r="H49"/>
     </row>
@@ -10473,10 +10473,10 @@
         <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>57.3281405082253</v>
+        <v>57.3281477801791</v>
       </c>
       <c r="H2" t="n">
-        <v>40.3536957324513</v>
+        <v>40.3536922096008</v>
       </c>
     </row>
     <row r="3">
@@ -10499,7 +10499,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>31.1608311737856</v>
+        <v>31.1608281680983</v>
       </c>
       <c r="H3"/>
     </row>
@@ -10523,7 +10523,7 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>8.10635960191601</v>
+        <v>8.10635394396169</v>
       </c>
       <c r="H4"/>
     </row>
@@ -10547,7 +10547,7 @@
         <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>2.98313940681246</v>
+        <v>2.98314090517806</v>
       </c>
       <c r="H5"/>
     </row>
@@ -10571,7 +10571,7 @@
         <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.42152930926069</v>
+        <v>0.421529202582811</v>
       </c>
       <c r="H6"/>
     </row>
@@ -10632,10 +10632,10 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>94.0187702741291</v>
+        <v>94.0396963929599</v>
       </c>
       <c r="H2" t="n">
-        <v>29.8363407254187</v>
+        <v>29.8417603709548</v>
       </c>
     </row>
     <row r="3">
@@ -10658,10 +10658,10 @@
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.46890703144531</v>
+        <v>2.46278487288434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08710525321409</v>
+        <v>0.0870575126095609</v>
       </c>
     </row>
     <row r="4">
@@ -10684,10 +10684,10 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>0.760679645127287</v>
+        <v>0.759402820259848</v>
       </c>
       <c r="H4" t="n">
-        <v>0.116497598478017</v>
+        <v>0.116513645389048</v>
       </c>
     </row>
     <row r="5">
@@ -10710,10 +10710,10 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>0.570724366816388</v>
+        <v>0.567713398141494</v>
       </c>
       <c r="H5" t="n">
-        <v>0.388472017279955</v>
+        <v>0.386431784779191</v>
       </c>
     </row>
     <row r="6">
@@ -10736,10 +10736,10 @@
         <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>0.425316442856433</v>
+        <v>0.422812373434628</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0199609849779236</v>
+        <v>0.0198434714759365</v>
       </c>
     </row>
     <row r="7">
@@ -10762,7 +10762,7 @@
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>0.362943249913339</v>
+        <v>0.362226789991755</v>
       </c>
       <c r="H7"/>
     </row>
@@ -10786,10 +10786,10 @@
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.237303217074989</v>
+        <v>0.23590627630397</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0202267483024398</v>
+        <v>0.0201076901838695</v>
       </c>
     </row>
     <row r="9">
@@ -10812,10 +10812,10 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.199192433748206</v>
+        <v>0.198019888344106</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0222951020193061</v>
+        <v>0.0221638051926366</v>
       </c>
     </row>
     <row r="10">
@@ -10838,10 +10838,10 @@
         <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>0.190898338682771</v>
+        <v>0.190677332152804</v>
       </c>
       <c r="H10" t="n">
-        <v>0.064368226732903</v>
+        <v>0.0644377307378925</v>
       </c>
     </row>
     <row r="11">
@@ -10864,10 +10864,10 @@
         <v>87</v>
       </c>
       <c r="G11" t="n">
-        <v>0.142788171635953</v>
+        <v>0.141947808790897</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0318242838983415</v>
+        <v>0.0316369585666598</v>
       </c>
     </row>
     <row r="12">
@@ -10890,10 +10890,10 @@
         <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>0.105694253405797</v>
+        <v>0.105071841369835</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00655903092408336</v>
+        <v>0.00652037608813461</v>
       </c>
     </row>
     <row r="13">
@@ -10916,10 +10916,10 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0818111706369464</v>
+        <v>0.0813294628481086</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0110361643657286</v>
+        <v>0.0109712459676748</v>
       </c>
     </row>
     <row r="14">
@@ -10942,10 +10942,10 @@
         <v>111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0660585929738167</v>
+        <v>0.0656698226017681</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0127913561117006</v>
+        <v>0.0127160107463229</v>
       </c>
     </row>
     <row r="15">
@@ -10968,10 +10968,10 @@
         <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0518306821460141</v>
+        <v>0.0515256044852872</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0107792383840783</v>
+        <v>0.0107159477595823</v>
       </c>
     </row>
     <row r="16">
@@ -10994,10 +10994,10 @@
         <v>101</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0299804884909323</v>
+        <v>0.0298040670411648</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00826426118102878</v>
+        <v>0.00821557962339601</v>
       </c>
     </row>
     <row r="17">
@@ -11020,10 +11020,10 @@
         <v>117</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0243908845075512</v>
+        <v>0.024247380112784</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00221492775885409</v>
+        <v>0.00220192113925494</v>
       </c>
     </row>
     <row r="18">
@@ -11046,10 +11046,10 @@
         <v>147</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02388287249898</v>
+        <v>0.023742169843383</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00467103303641761</v>
+        <v>0.00464364622282581</v>
       </c>
     </row>
     <row r="19">
@@ -11072,10 +11072,10 @@
         <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0213419713766395</v>
+        <v>0.0212165358530648</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00881592715433516</v>
+        <v>0.00876410834067219</v>
       </c>
     </row>
     <row r="20">
@@ -11098,10 +11098,10 @@
         <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0208339593680683</v>
+        <v>0.0207113255836637</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0057113585077658</v>
+        <v>0.00567783010644786</v>
       </c>
     </row>
     <row r="21">
@@ -11124,10 +11124,10 @@
         <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>0.020325737089626</v>
+        <v>0.0202061153142627</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0071863076059706</v>
+        <v>0.00714401435901212</v>
       </c>
     </row>
     <row r="22">
@@ -11150,7 +11150,7 @@
         <v>125</v>
       </c>
       <c r="G22" t="n">
-        <v>0.018293268515599</v>
+        <v>0.0181854829150021</v>
       </c>
       <c r="H22"/>
     </row>
@@ -11174,7 +11174,7 @@
         <v>133</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0177850462371566</v>
+        <v>0.0176802726456011</v>
       </c>
       <c r="H23"/>
     </row>
@@ -11198,7 +11198,7 @@
         <v>134</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0142281210976738</v>
+        <v>0.0141442181164809</v>
       </c>
       <c r="H24"/>
     </row>
@@ -11222,7 +11222,7 @@
         <v>110</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0137198988192314</v>
+        <v>0.0136390078470799</v>
       </c>
       <c r="H25"/>
     </row>
@@ -11246,7 +11246,7 @@
         <v>112</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0127036645322179</v>
+        <v>0.0126287959866213</v>
       </c>
       <c r="H26"/>
     </row>
@@ -11270,7 +11270,7 @@
         <v>148</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0121954422537756</v>
+        <v>0.0121235857172203</v>
       </c>
       <c r="H27"/>
     </row>
@@ -11294,7 +11294,7 @@
         <v>104</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0116872199753333</v>
+        <v>0.0116185841261627</v>
       </c>
       <c r="H28"/>
     </row>
@@ -11318,10 +11318,10 @@
         <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0106709856883198</v>
+        <v>0.0106083722657041</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00176029081686764</v>
+        <v>0.00174985874922072</v>
       </c>
     </row>
     <row r="30">
@@ -11344,7 +11344,7 @@
         <v>83</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00965475140130624</v>
+        <v>0.00959795172690207</v>
       </c>
       <c r="H30"/>
     </row>
@@ -11353,50 +11353,50 @@
         <v>143</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="G31" t="n">
-        <v>0.00762228282727919</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00107795357505818</v>
-      </c>
+        <v>0.00757731932764146</v>
+      </c>
+      <c r="H31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
         <v>143</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00762207255740809</v>
-      </c>
-      <c r="H32"/>
+        <v>0.00757711064929804</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00107156526438389</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -11418,7 +11418,7 @@
         <v>152</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="H33"/>
     </row>
@@ -11442,7 +11442,7 @@
         <v>107</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="H34"/>
     </row>
@@ -11466,7 +11466,7 @@
         <v>127</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00660583827039457</v>
+        <v>0.00656689878883944</v>
       </c>
       <c r="H35"/>
     </row>
@@ -11490,7 +11490,7 @@
         <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00609782626182335</v>
+        <v>0.00606189719778185</v>
       </c>
       <c r="H36"/>
     </row>
@@ -11514,7 +11514,7 @@
         <v>126</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00508138170493873</v>
+        <v>0.00505147665897983</v>
       </c>
       <c r="H37"/>
     </row>
@@ -11538,7 +11538,7 @@
         <v>121</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00355692513948289</v>
+        <v>0.00353605452912022</v>
       </c>
       <c r="H38"/>
     </row>
@@ -11562,7 +11562,7 @@
         <v>88</v>
       </c>
       <c r="G39" t="n">
-        <v>0.00254069085246936</v>
+        <v>0.00252584266866162</v>
       </c>
       <c r="H39"/>
     </row>
@@ -11586,7 +11586,7 @@
         <v>154</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00203267884389815</v>
+        <v>0.00202063239926062</v>
       </c>
       <c r="H40"/>
     </row>
@@ -11647,10 +11647,10 @@
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>25.1964424022149</v>
+        <v>25.1965367592767</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93523792598481</v>
+        <v>1.93543404111971</v>
       </c>
     </row>
     <row r="3">
@@ -11673,10 +11673,10 @@
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>18.1689234804074</v>
+        <v>18.1673264885753</v>
       </c>
       <c r="H3" t="n">
-        <v>0.432739320612276</v>
+        <v>0.432718841054423</v>
       </c>
     </row>
     <row r="4">
@@ -11699,10 +11699,10 @@
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>11.2867641756239</v>
+        <v>11.2870459326145</v>
       </c>
       <c r="H4" t="n">
-        <v>7.79747841092047</v>
+        <v>7.79773733744146</v>
       </c>
     </row>
     <row r="5">
@@ -11725,10 +11725,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>8.0097858428954</v>
+        <v>8.01115393796449</v>
       </c>
       <c r="H5" t="n">
-        <v>1.60905995460106</v>
+        <v>1.60936124402573</v>
       </c>
     </row>
     <row r="6">
@@ -11751,10 +11751,10 @@
         <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>6.77989306604406</v>
+        <v>6.77881974051897</v>
       </c>
       <c r="H6" t="n">
-        <v>1.16354430973066</v>
+        <v>1.16335433995446</v>
       </c>
     </row>
     <row r="7">
@@ -11777,10 +11777,10 @@
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>4.87573278327654</v>
+        <v>4.87725512036695</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0993527028685948</v>
+        <v>0.099401333768649</v>
       </c>
     </row>
     <row r="8">
@@ -11803,10 +11803,10 @@
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>4.36324664897001</v>
+        <v>4.36332007175648</v>
       </c>
       <c r="H8" t="n">
-        <v>0.534854245506558</v>
+        <v>0.534909041154877</v>
       </c>
     </row>
     <row r="9">
@@ -11829,10 +11829,10 @@
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>4.17942439810022</v>
+        <v>4.17865556908465</v>
       </c>
       <c r="H9" t="n">
-        <v>0.629474802709262</v>
+        <v>0.629336454614041</v>
       </c>
     </row>
     <row r="10">
@@ -11855,10 +11855,10 @@
         <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7812086367447</v>
+        <v>2.78086546106678</v>
       </c>
       <c r="H10" t="n">
-        <v>0.241037391606985</v>
+        <v>0.240987580928254</v>
       </c>
     </row>
     <row r="11">
@@ -11881,10 +11881,10 @@
         <v>107</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65381557600859</v>
+        <v>2.65389443500849</v>
       </c>
       <c r="H11" t="n">
-        <v>1.10004303459688</v>
+        <v>1.1000766666257</v>
       </c>
     </row>
     <row r="12">
@@ -11907,10 +11907,10 @@
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>1.75956025425825</v>
+        <v>1.75958608100551</v>
       </c>
       <c r="H12" t="n">
-        <v>0.115464162238769</v>
+        <v>0.115450531966808</v>
       </c>
     </row>
     <row r="13">
@@ -11933,10 +11933,10 @@
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>1.63554415932806</v>
+        <v>1.63559752828711</v>
       </c>
       <c r="H13" t="n">
-        <v>0.122376670856706</v>
+        <v>0.122374919760594</v>
       </c>
     </row>
     <row r="14">
@@ -11959,10 +11959,10 @@
         <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>1.54503415439421</v>
+        <v>1.54499986880777</v>
       </c>
       <c r="H14" t="n">
-        <v>0.250650727927502</v>
+        <v>0.250653674269885</v>
       </c>
     </row>
     <row r="15">
@@ -11985,10 +11985,10 @@
         <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0631987894026</v>
+        <v>1.06308706922884</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0927383291354896</v>
+        <v>0.0927261331216983</v>
       </c>
     </row>
     <row r="16">
@@ -12011,10 +12011,10 @@
         <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>0.897465727183185</v>
+        <v>0.897466482214415</v>
       </c>
       <c r="H16" t="n">
-        <v>0.461719332595731</v>
+        <v>0.461701075394256</v>
       </c>
     </row>
     <row r="17">
@@ -12037,10 +12037,10 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.57047476881237</v>
+        <v>0.570547149921031</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0747425037899925</v>
+        <v>0.0747481597976273</v>
       </c>
     </row>
     <row r="18">
@@ -12063,10 +12063,10 @@
         <v>87</v>
       </c>
       <c r="G18" t="n">
-        <v>0.541242508169327</v>
+        <v>0.541432354961316</v>
       </c>
       <c r="H18" t="n">
-        <v>0.237512932641943</v>
+        <v>0.237616433436933</v>
       </c>
     </row>
     <row r="19">
@@ -12089,10 +12089,10 @@
         <v>147</v>
       </c>
       <c r="G19" t="n">
-        <v>0.524260671449889</v>
+        <v>0.524152306972405</v>
       </c>
       <c r="H19" t="n">
-        <v>0.323530587624025</v>
+        <v>0.323469312291106</v>
       </c>
     </row>
     <row r="20">
@@ -12115,10 +12115,10 @@
         <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>0.437457092400592</v>
+        <v>0.437680707236282</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0974223302537888</v>
+        <v>0.0974726660697121</v>
       </c>
     </row>
     <row r="21">
@@ -12141,10 +12141,10 @@
         <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>0.297590307020918</v>
+        <v>0.297553863194058</v>
       </c>
       <c r="H21" t="n">
-        <v>0.105589392066944</v>
+        <v>0.105597733144794</v>
       </c>
     </row>
     <row r="22">
@@ -12167,10 +12167,10 @@
         <v>77</v>
       </c>
       <c r="G22" t="n">
-        <v>0.25487580782696</v>
+        <v>0.254814837259604</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0191447711243624</v>
+        <v>0.0191428227718087</v>
       </c>
     </row>
     <row r="23">
@@ -12193,7 +12193,7 @@
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>0.253991756615979</v>
+        <v>0.253949371069562</v>
       </c>
       <c r="H23"/>
     </row>
@@ -12217,7 +12217,7 @@
         <v>156</v>
       </c>
       <c r="G24" t="n">
-        <v>0.181624020011844</v>
+        <v>0.181564926084247</v>
       </c>
       <c r="H24"/>
     </row>
@@ -12241,10 +12241,10 @@
         <v>86</v>
       </c>
       <c r="G25" t="n">
-        <v>0.173577872758271</v>
+        <v>0.173568969952148</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0241654040245121</v>
+        <v>0.0241653376278085</v>
       </c>
     </row>
     <row r="26">
@@ -12267,7 +12267,7 @@
         <v>74</v>
       </c>
       <c r="G26" t="n">
-        <v>0.16432736588394</v>
+        <v>0.164414789510755</v>
       </c>
       <c r="H26"/>
     </row>
@@ -12291,10 +12291,10 @@
         <v>130</v>
       </c>
       <c r="G27" t="n">
-        <v>0.156667419055868</v>
+        <v>0.156728059142117</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0238887665894522</v>
+        <v>0.0238873408762922</v>
       </c>
     </row>
     <row r="28">
@@ -12317,7 +12317,7 @@
         <v>111</v>
       </c>
       <c r="G28" t="n">
-        <v>0.137005973696932</v>
+        <v>0.137063862219539</v>
       </c>
       <c r="H28"/>
     </row>
@@ -12341,10 +12341,10 @@
         <v>137</v>
       </c>
       <c r="G29" t="n">
-        <v>0.125886696043279</v>
+        <v>0.12594820237915</v>
       </c>
       <c r="H29" t="n">
-        <v>0.010537225521728</v>
+        <v>0.0105463945417804</v>
       </c>
     </row>
     <row r="30">
@@ -12367,7 +12367,7 @@
         <v>134</v>
       </c>
       <c r="G30" t="n">
-        <v>0.122247992508224</v>
+        <v>0.122261279814807</v>
       </c>
       <c r="H30"/>
     </row>
@@ -12376,50 +12376,50 @@
         <v>155</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F31" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="G31" t="n">
-        <v>0.11370582480294</v>
-      </c>
-      <c r="H31"/>
+        <v>0.113714572470864</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0203644825135999</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
         <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11370582480294</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.020369505421689</v>
-      </c>
+        <v>0.113712742732618</v>
+      </c>
+      <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -12441,10 +12441,10 @@
         <v>117</v>
       </c>
       <c r="G33" t="n">
-        <v>0.108551604906202</v>
+        <v>0.108576667477973</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0205206678670958</v>
+        <v>0.0205241840114384</v>
       </c>
     </row>
     <row r="34">
@@ -12467,7 +12467,7 @@
         <v>106</v>
       </c>
       <c r="G34" t="n">
-        <v>0.107491841653286</v>
+        <v>0.10745686767183</v>
       </c>
       <c r="H34"/>
     </row>
@@ -12491,10 +12491,10 @@
         <v>36</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0971852321935793</v>
+        <v>0.0971847171625386</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0203933620660771</v>
+        <v>0.0203647318536465</v>
       </c>
     </row>
     <row r="36">
@@ -12517,7 +12517,7 @@
         <v>157</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0741321783585579</v>
+        <v>0.0741080584124175</v>
       </c>
       <c r="H36"/>
     </row>
@@ -12541,7 +12541,7 @@
         <v>88</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0381954051154606</v>
+        <v>0.0381921263948049</v>
       </c>
       <c r="H37"/>
     </row>
@@ -12565,10 +12565,10 @@
         <v>128</v>
       </c>
       <c r="G38" t="n">
-        <v>0.037313184238249</v>
+        <v>0.0373284899430084</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0159010500948038</v>
+        <v>0.0159152837694857</v>
       </c>
     </row>
     <row r="39">
@@ -12591,7 +12591,7 @@
         <v>56</v>
       </c>
       <c r="G39" t="n">
-        <v>0.037066089179279</v>
+        <v>0.0370540292062087</v>
       </c>
       <c r="H39"/>
     </row>
@@ -12615,7 +12615,7 @@
         <v>122</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0296532374101772</v>
+        <v>0.029643589312616</v>
       </c>
       <c r="H40"/>
     </row>
@@ -12639,7 +12639,7 @@
         <v>73</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0222403856410754</v>
+        <v>0.0222331494190234</v>
       </c>
       <c r="H41"/>
     </row>
@@ -12663,7 +12663,7 @@
         <v>24</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0222403856410754</v>
+        <v>0.0222331494190234</v>
       </c>
       <c r="H42"/>
     </row>
@@ -12687,7 +12687,7 @@
         <v>158</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0213581647638638</v>
+        <v>0.0213713427054722</v>
       </c>
       <c r="H43"/>
     </row>
@@ -12711,7 +12711,7 @@
         <v>159</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0185339597565246</v>
+        <v>0.018527929472227</v>
       </c>
       <c r="H44"/>
     </row>
@@ -12735,7 +12735,7 @@
         <v>131</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0128141667248102</v>
+        <v>0.0128228056232833</v>
       </c>
       <c r="H45"/>
     </row>
@@ -12759,7 +12759,7 @@
         <v>160</v>
       </c>
       <c r="G46" t="n">
-        <v>0.00854216770528344</v>
+        <v>0.00854853708218889</v>
       </c>
       <c r="H46"/>
     </row>
